--- a/data/trans_camb/IP16A02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 27,0</t>
+          <t>-20,07; 25,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 24,12</t>
+          <t>-23,48; 24,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 21,52</t>
+          <t>-40,65; 20,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 17,35</t>
+          <t>-33,69; 14,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 26,14</t>
+          <t>-31,73; 26,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 24,9</t>
+          <t>-28,9; 27,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 15,77</t>
+          <t>-17,82; 15,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 18,93</t>
+          <t>-20,23; 19,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 15,83</t>
+          <t>-26,47; 18,26</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 125,42</t>
+          <t>-44,18; 114,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 114,71</t>
+          <t>-52,76; 107,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-88,16; 76,83</t>
+          <t>-85,11; 68,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,48; 55,04</t>
+          <t>-56,16; 44,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,38; 79,6</t>
+          <t>-57,36; 87,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 73,12</t>
+          <t>-52,8; 79,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 53,45</t>
+          <t>-38,35; 50,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 59,99</t>
+          <t>-42,87; 62,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,71; 45,46</t>
+          <t>-55,62; 57,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 22,51</t>
+          <t>0,06; 23,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 15,76</t>
+          <t>-6,55; 15,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 21,22</t>
+          <t>-17,33; 21,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 15,27</t>
+          <t>-4,94; 16,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 8,71</t>
+          <t>-14,77; 8,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 14,85</t>
+          <t>-7,6; 15,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 16,0</t>
+          <t>1,21; 16,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 8,61</t>
+          <t>-6,76; 8,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 13,89</t>
+          <t>-9,09; 13,6</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 86,87</t>
+          <t>0,16; 87,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 62,28</t>
+          <t>-17,01; 58,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 70,88</t>
+          <t>-46,06; 73,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 50,48</t>
+          <t>-11,65; 55,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 30,25</t>
+          <t>-33,8; 27,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 49,8</t>
+          <t>-17,85; 51,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 53,71</t>
+          <t>3,08; 53,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 28,89</t>
+          <t>-17,67; 29,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 43,68</t>
+          <t>-23,07; 43,03</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 25,48</t>
+          <t>-14,55; 25,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 31,55</t>
+          <t>-10,4; 31,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 38,09</t>
+          <t>-4,97; 35,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 0,26</t>
+          <t>-35,59; 0,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 12,23</t>
+          <t>-23,56; 14,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 24,62</t>
+          <t>-14,49; 24,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 5,58</t>
+          <t>-20,97; 5,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 14,05</t>
+          <t>-14,14; 13,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 22,34</t>
+          <t>-5,17; 22,9</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 139,0</t>
+          <t>-32,01; 146,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 164,21</t>
+          <t>-23,21; 167,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 189,49</t>
+          <t>-13,05; 185,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 3,51</t>
+          <t>-61,98; 1,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 32,91</t>
+          <t>-41,24; 37,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 64,26</t>
+          <t>-25,59; 63,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,5; 16,89</t>
+          <t>-42,88; 15,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 40,88</t>
+          <t>-27,78; 39,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 64,91</t>
+          <t>-10,59; 66,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 17,1</t>
+          <t>0,06; 17,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 14,89</t>
+          <t>-3,73; 15,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 18,9</t>
+          <t>-10,11; 20,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 6,76</t>
+          <t>-10,75; 6,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 4,72</t>
+          <t>-14,36; 4,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 12,39</t>
+          <t>-6,88; 11,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 9,65</t>
+          <t>-3,03; 9,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 6,66</t>
+          <t>-6,03; 6,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 12,33</t>
+          <t>-6,01; 12,49</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 61,31</t>
+          <t>0,13; 65,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 55,65</t>
+          <t>-10,11; 53,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 61,75</t>
+          <t>-27,65; 68,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 17,88</t>
+          <t>-23,3; 19,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 13,26</t>
+          <t>-30,93; 13,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 34,45</t>
+          <t>-15,31; 33,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 28,93</t>
+          <t>-7,71; 27,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 19,96</t>
+          <t>-15,18; 20,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 35,34</t>
+          <t>-14,66; 36,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 25,76</t>
+          <t>-20,43; 26,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 24,65</t>
+          <t>-24,8; 24,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 20,39</t>
+          <t>-43,47; 21,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,69; 14,93</t>
+          <t>-30,78; 16,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 26,13</t>
+          <t>-32,39; 28,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 27,94</t>
+          <t>-30,45; 27,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 15,03</t>
+          <t>-17,45; 15,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 19,21</t>
+          <t>-18,71; 18,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 18,26</t>
+          <t>-25,62; 16,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,18; 114,38</t>
+          <t>-43,41; 122,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 107,95</t>
+          <t>-53,45; 114,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,11; 68,7</t>
+          <t>-86,26; 77,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 44,28</t>
+          <t>-53,74; 53,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,36; 87,09</t>
+          <t>-56,37; 83,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,8; 79,65</t>
+          <t>-53,18; 85,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,35; 50,82</t>
+          <t>-37,0; 52,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 62,18</t>
+          <t>-39,95; 60,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,62; 57,1</t>
+          <t>-54,81; 50,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 23,45</t>
+          <t>0,62; 23,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 15,18</t>
+          <t>-5,47; 17,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 21,36</t>
+          <t>-13,65; 21,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 16,19</t>
+          <t>-5,44; 16,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 8,21</t>
+          <t>-15,22; 8,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 15,22</t>
+          <t>-7,71; 15,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 16,43</t>
+          <t>1,06; 16,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 8,87</t>
+          <t>-7,37; 9,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 13,6</t>
+          <t>-8,1; 14,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 87,64</t>
+          <t>2,05; 87,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 58,3</t>
+          <t>-14,6; 69,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,06; 73,14</t>
+          <t>-36,07; 75,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 55,03</t>
+          <t>-12,98; 58,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 27,43</t>
+          <t>-36,0; 29,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 51,73</t>
+          <t>-18,53; 52,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 53,23</t>
+          <t>2,27; 55,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 29,11</t>
+          <t>-18,24; 29,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 43,03</t>
+          <t>-22,97; 45,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 25,42</t>
+          <t>-14,9; 23,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 31,61</t>
+          <t>-10,15; 31,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 35,47</t>
+          <t>-2,25; 35,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 0,63</t>
+          <t>-34,27; -0,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 14,37</t>
+          <t>-23,38; 13,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 24,82</t>
+          <t>-15,41; 23,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 5,29</t>
+          <t>-21,86; 5,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 13,35</t>
+          <t>-12,64; 15,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 22,9</t>
+          <t>-4,9; 22,93</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 146,69</t>
+          <t>-32,7; 118,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 167,17</t>
+          <t>-24,7; 157,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 185,46</t>
+          <t>-5,9; 176,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,98; 1,82</t>
+          <t>-60,79; -0,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 37,52</t>
+          <t>-40,72; 34,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 63,46</t>
+          <t>-26,08; 56,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 15,58</t>
+          <t>-43,3; 16,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 39,41</t>
+          <t>-26,73; 46,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 66,1</t>
+          <t>-9,62; 67,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 17,94</t>
+          <t>-0,03; 17,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 15,16</t>
+          <t>-3,18; 14,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 20,0</t>
+          <t>-11,52; 18,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 6,76</t>
+          <t>-10,58; 6,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 4,76</t>
+          <t>-13,7; 4,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 11,98</t>
+          <t>-6,81; 12,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 9,5</t>
+          <t>-3,11; 9,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 6,89</t>
+          <t>-5,76; 7,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 12,49</t>
+          <t>-5,9; 12,37</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 65,25</t>
+          <t>-0,2; 63,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 53,88</t>
+          <t>-8,35; 50,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 68,1</t>
+          <t>-29,72; 63,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 19,0</t>
+          <t>-23,02; 18,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 13,04</t>
+          <t>-29,77; 11,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 33,55</t>
+          <t>-15,08; 34,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 27,32</t>
+          <t>-7,49; 29,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 20,25</t>
+          <t>-14,12; 22,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 36,61</t>
+          <t>-13,89; 36,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-7,71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,53</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,87</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-9,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,53</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,97</t>
+          <t>4,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 26,12</t>
+          <t>-30,72; 17,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 24,71</t>
+          <t>-30,51; 26,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 21,18</t>
+          <t>-27,92; 28,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 16,82</t>
+          <t>-19,72; 27,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 28,07</t>
+          <t>-23,19; 24,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 27,13</t>
+          <t>-27,14; 35,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 15,78</t>
+          <t>-18,06; 15,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 18,15</t>
+          <t>-20,01; 18,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 16,45</t>
+          <t>-16,32; 24,75</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-16,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-5,49%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>10,6%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-26,27%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-16,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-5,49%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-3,42%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-12,37%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 122,5</t>
+          <t>-53,48; 55,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 114,56</t>
+          <t>-56,38; 79,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-86,26; 77,3</t>
+          <t>-50,35; 81,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 53,68</t>
+          <t>-44,04; 125,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 83,28</t>
+          <t>-52,93; 114,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,18; 85,23</t>
+          <t>-61,04; 156,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 52,46</t>
+          <t>-37,01; 53,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,95; 60,02</t>
+          <t>-42,05; 59,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,81; 50,5</t>
+          <t>-35,83; 77,57</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,85</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,22</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,81</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,85</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>17,13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>9,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 23,05</t>
+          <t>-6,19; 15,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 17,73</t>
+          <t>-13,19; 8,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 21,69</t>
+          <t>-8,71; 14,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 16,55</t>
+          <t>-0,41; 22,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 8,31</t>
+          <t>-6,26; 15,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 15,58</t>
+          <t>3,35; 28,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 16,64</t>
+          <t>0,87; 16,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 9,04</t>
+          <t>-6,35; 8,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 14,47</t>
+          <t>0,82; 18,24</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-7,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>36,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>14,72%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-7,82%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 87,95</t>
+          <t>-14,19; 50,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 69,97</t>
+          <t>-32,29; 30,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 75,11</t>
+          <t>-20,96; 47,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 58,47</t>
+          <t>-1,16; 86,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 29,07</t>
+          <t>-16,09; 62,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 52,89</t>
+          <t>7,8; 103,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 55,62</t>
+          <t>2,21; 53,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 29,63</t>
+          <t>-16,29; 28,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 45,34</t>
+          <t>1,69; 58,9</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-17,84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,03</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,99</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>11,26</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17,46</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-17,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,6</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>16,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>8,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 23,43</t>
+          <t>-36,1; 0,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 31,65</t>
+          <t>-26,06; 12,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 35,81</t>
+          <t>-15,54; 25,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,27; -0,06</t>
+          <t>-13,5; 25,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 13,24</t>
+          <t>-10,3; 31,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 23,46</t>
+          <t>-3,5; 37,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 5,21</t>
+          <t>-21,71; 5,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 15,44</t>
+          <t>-14,19; 14,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 22,93</t>
+          <t>-5,83; 22,18</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-36,35%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-13,45%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>15,41%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>34,78%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>53,93%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-36,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-13,45%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 118,1</t>
+          <t>-60,04; 3,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 157,75</t>
+          <t>-43,55; 32,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 176,72</t>
+          <t>-26,03; 65,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,79; -0,27</t>
+          <t>-32,65; 139,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 34,02</t>
+          <t>-22,76; 164,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 56,66</t>
+          <t>-8,57; 186,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,3; 16,03</t>
+          <t>-43,5; 16,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 46,02</t>
+          <t>-27,31; 40,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 67,94</t>
+          <t>-12,11; 63,96</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,04</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,99</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5,74</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,29</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,19</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>15,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>8,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 17,8</t>
+          <t>-11,03; 6,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 14,37</t>
+          <t>-13,45; 4,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 18,84</t>
+          <t>-6,55; 12,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 6,75</t>
+          <t>-0,53; 17,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 4,21</t>
+          <t>-2,4; 14,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 12,41</t>
+          <t>5,79; 24,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 9,79</t>
+          <t>-2,92; 9,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 7,42</t>
+          <t>-6,42; 6,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 12,37</t>
+          <t>2,46; 15,26</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,68%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-10,24%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>27,29%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>17,41%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-4,68%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-10,24%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 63,21</t>
+          <t>-23,87; 17,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 50,83</t>
+          <t>-29,33; 13,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 63,66</t>
+          <t>-14,41; 35,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 18,23</t>
+          <t>-1,21; 61,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 11,62</t>
+          <t>-6,92; 55,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 34,94</t>
+          <t>16,42; 90,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 29,71</t>
+          <t>-7,2; 28,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 22,19</t>
+          <t>-15,45; 19,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 36,84</t>
+          <t>6,12; 45,13</t>
         </is>
       </c>
     </row>
